--- a/fundraiser_forms/007_fundraising_gala_registration_form--fundraiser_forms.xlsx
+++ b/fundraiser_forms/007_fundraising_gala_registration_form--fundraiser_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -441,7 +441,7 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
-    <col width="16" customWidth="1" min="2" max="2"/>
+    <col width="18" customWidth="1" min="2" max="2"/>
     <col width="19" customWidth="1" min="3" max="3"/>
     <col width="6" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
@@ -842,12 +842,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>ticket_price</t>
+          <t>ticket_price_2</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Ticket Price</t>
+          <t>Ticket Price 2</t>
         </is>
       </c>
       <c r="D18" t="inlineStr"/>
@@ -865,12 +865,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>num_tickets</t>
+          <t>num_tickets_2</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Number of Tickets</t>
+          <t>Num Tickets 2</t>
         </is>
       </c>
       <c r="D19" t="inlineStr"/>
@@ -888,12 +888,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>payment_amount</t>
+          <t>payment_amount_2</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Payment Amount</t>
+          <t>Payment Amount 2</t>
         </is>
       </c>
       <c r="D20" t="inlineStr"/>
@@ -911,12 +911,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>payment_method</t>
+          <t>payment_method_2</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Payment Method</t>
+          <t>Payment Method 2</t>
         </is>
       </c>
       <c r="D21" t="inlineStr"/>
@@ -940,9 +940,9 @@
   <dimension ref="A1:C8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="24" customWidth="1" min="1" max="1"/>
-    <col width="50" customWidth="1" min="2" max="2"/>
-    <col width="50" customWidth="1" min="3" max="3"/>
+    <col width="26" customWidth="1" min="1" max="1"/>
+    <col width="17" customWidth="1" min="2" max="2"/>
+    <col width="17" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -970,12 +970,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'name':_'credit_card',_'label':_'credit_card'}</t>
+          <t>credit_card</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'name': 'credit_card', 'label': 'Credit Card'}</t>
+          <t>Credit Card</t>
         </is>
       </c>
     </row>
@@ -987,12 +987,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'name':_'bank_transfer',_'label':_'bank_transfer'}</t>
+          <t>bank_transfer</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'name': 'bank_transfer', 'label': 'Bank Transfer'}</t>
+          <t>Bank Transfer</t>
         </is>
       </c>
     </row>
@@ -1004,12 +1004,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'name':_'vip_ticket',_'label':_'vip_ticket'}</t>
+          <t>vip_ticket</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'name': 'vip_ticket', 'label': 'Vip Ticket'}</t>
+          <t>Vip Ticket</t>
         </is>
       </c>
     </row>
@@ -1021,12 +1021,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'name':_'standard_ticket',_'label':_'standard_ticket'}</t>
+          <t>standard_ticket</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'name': 'standard_ticket', 'label': 'Standard Ticket'}</t>
+          <t>Standard Ticket</t>
         </is>
       </c>
     </row>
@@ -1038,46 +1038,46 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'name':_'premium_ticket',_'label':_'premium_ticket'}</t>
+          <t>premium_ticket</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'name': 'premium_ticket', 'label': 'Premium Ticket'}</t>
+          <t>Premium Ticket</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>payment_method_choices</t>
+          <t>payment_method_2_choices</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'name':_'credit_card',_'label':_'credit_card'}</t>
+          <t>credit_card</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'name': 'credit_card', 'label': 'Credit Card'}</t>
+          <t>Credit Card</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>payment_method_choices</t>
+          <t>payment_method_2_choices</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'name':_'bank_transfer',_'label':_'bank_transfer'}</t>
+          <t>bank_transfer</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'name': 'bank_transfer', 'label': 'Bank Transfer'}</t>
+          <t>Bank Transfer</t>
         </is>
       </c>
     </row>
